--- a/data/kz/01_cities.xlsx
+++ b/data/kz/01_cities.xlsx
@@ -587,7 +587,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AKT</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEM</t>
+          <t>semey</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>uralsk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1018,7 +1018,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,7 +1080,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAV</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KOS</t>
+          <t>kostanay</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1204,7 +1204,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KZO</t>
+          <t>kyzylorda</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ATY</t>
+          <t>atyrau</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,7 +1328,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AKA</t>
+          <t>aktau</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PET</t>
+          <t>petropavl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1452,7 +1452,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KOK</t>
+          <t>kokshetau</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
